--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16245" windowHeight="7065"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,7 +254,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/febrero de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/marzo de 2026</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="21" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B175" s="31">
         <v>-5.138214737095181</v>
@@ -3838,46 +3838,57 @@
         <v>-0.58755797637353169</v>
       </c>
     </row>
-    <row r="201" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A201" s="35" t="s">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A201" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B201" s="25">
+        <v>-1.4584831237162588</v>
+      </c>
+      <c r="C201" s="31">
+        <v>-2.0136773701644683</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A202" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B201" s="35"/>
-      <c r="C201" s="35"/>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A202" s="36" t="s">
+      <c r="B202" s="35"/>
+      <c r="C202" s="35"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A203" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B202" s="36"/>
-      <c r="C202" s="36"/>
-      <c r="D202" s="30"/>
-      <c r="E202" s="30"/>
-      <c r="F202" s="30"/>
-      <c r="H202" s="30"/>
-      <c r="I202" s="30"/>
-      <c r="J202" s="30"/>
-    </row>
-    <row r="203" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="34" t="s">
+      <c r="B203" s="36"/>
+      <c r="C203" s="36"/>
+      <c r="D203" s="30"/>
+      <c r="E203" s="30"/>
+      <c r="F203" s="30"/>
+      <c r="H203" s="30"/>
+      <c r="I203" s="30"/>
+      <c r="J203" s="30"/>
+    </row>
+    <row r="204" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B203" s="34"/>
-      <c r="C203" s="34"/>
-    </row>
-    <row r="204" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="33" t="s">
+      <c r="B204" s="34"/>
+      <c r="C204" s="34"/>
+    </row>
+    <row r="205" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B204" s="33"/>
-      <c r="C204" s="33"/>
+      <c r="B205" s="33"/>
+      <c r="C205" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A204:C204"/>
+    <mergeCell ref="A202:C202"/>
     <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A202:C202"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3989,7 +4000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -3997,7 +4008,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>

--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\SUPERMERCADOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,7 +254,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/marzo de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/abril de 2026</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="21" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B176" s="31">
         <v>-11.14605258779482</v>
@@ -3849,46 +3849,57 @@
         <v>-2.0136773701644683</v>
       </c>
     </row>
-    <row r="202" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A202" s="35" t="s">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A202" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B202" s="25">
+        <v>-0.76856188125520308</v>
+      </c>
+      <c r="C202" s="31">
+        <v>-1.3788194803648346</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A203" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B202" s="35"/>
-      <c r="C202" s="35"/>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A203" s="36" t="s">
+      <c r="B203" s="35"/>
+      <c r="C203" s="35"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A204" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B203" s="36"/>
-      <c r="C203" s="36"/>
-      <c r="D203" s="30"/>
-      <c r="E203" s="30"/>
-      <c r="F203" s="30"/>
-      <c r="H203" s="30"/>
-      <c r="I203" s="30"/>
-      <c r="J203" s="30"/>
-    </row>
-    <row r="204" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="34" t="s">
+      <c r="B204" s="36"/>
+      <c r="C204" s="36"/>
+      <c r="D204" s="30"/>
+      <c r="E204" s="30"/>
+      <c r="F204" s="30"/>
+      <c r="H204" s="30"/>
+      <c r="I204" s="30"/>
+      <c r="J204" s="30"/>
+    </row>
+    <row r="205" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B204" s="34"/>
-      <c r="C204" s="34"/>
-    </row>
-    <row r="205" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="33" t="s">
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B205" s="33"/>
-      <c r="C205" s="33"/>
+      <c r="B206" s="33"/>
+      <c r="C206" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3959,7 +3970,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3967,7 +3978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
@@ -4000,7 +4011,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -4008,7 +4019,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>

--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,7 +254,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/abril de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/mayo de 2026</t>
   </si>
 </sst>
 </file>
@@ -971,7 +971,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="37"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="36" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1040,9 +1040,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1053,6 +1050,12 @@
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1442,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
@@ -1640,39 +1643,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="41"/>
+      <c r="C2" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="43"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="20">
@@ -1711,7 +1714,7 @@
       <c r="A8" s="20">
         <v>2004</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="31">
         <v>5.6677534891249604</v>
       </c>
       <c r="C8" s="24" t="s">
@@ -1722,7 +1725,7 @@
       <c r="A9" s="20">
         <v>2005</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="31">
         <v>3.6719150054694838</v>
       </c>
       <c r="C9" s="24" t="s">
@@ -1733,7 +1736,7 @@
       <c r="A10" s="20">
         <v>2006</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="31">
         <v>5.0116728157364898</v>
       </c>
       <c r="C10" s="24" t="s">
@@ -1744,7 +1747,7 @@
       <c r="A11" s="20">
         <v>2007</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="31">
         <v>11.149289927539275</v>
       </c>
       <c r="C11" s="24" t="s">
@@ -1755,7 +1758,7 @@
       <c r="A12" s="20">
         <v>2008</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="31">
         <v>22.742185794753045</v>
       </c>
       <c r="C12" s="24" t="s">
@@ -1766,7 +1769,7 @@
       <c r="A13" s="20">
         <v>2009</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="31">
         <v>10.294757495636308</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -1777,7 +1780,7 @@
       <c r="A14" s="20">
         <v>2010</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="31">
         <v>13.990244583403278</v>
       </c>
       <c r="C14" s="24" t="s">
@@ -1788,7 +1791,7 @@
       <c r="A15" s="20">
         <v>2011</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="31">
         <v>11.325208607111993</v>
       </c>
       <c r="C15" s="24" t="s">
@@ -1799,142 +1802,142 @@
       <c r="A16" s="20">
         <v>2012</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="31">
         <v>13.485588386808889</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="32" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="30">
         <v>12.267324232402398</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="30">
         <v>14.95400381428853</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="30">
         <v>14.38102290254022</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="30">
         <v>9.6242409705554088</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="30">
         <v>7.5181052233210366</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="30">
         <v>15.082435351028135</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="30">
         <v>11.254800062963799</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="30">
         <v>14.580237947621356</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="30">
         <v>17.375228746946526</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="30">
         <v>12.579843654386313</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="30">
         <v>14.966764521171584</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="30">
         <v>16.676475631471654</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="33" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1942,142 +1945,142 @@
       <c r="A29" s="20">
         <v>2013</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="31">
         <v>17.774293863248758</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="32" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="30">
         <v>15.872583851024501</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="30">
         <v>15.485648312155531</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="30">
         <v>16.655521469843706</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="30">
         <v>12.625044620490012</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="30">
         <v>23.339021657045201</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="30">
         <v>18.178382486690616</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="30">
         <v>15.344902202564903</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="30">
         <v>0.59748211022692121</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="30">
         <v>18.388819223324514</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="30">
         <v>2.4181983417348674</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="30">
         <v>13.971017448071187</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="30">
         <v>-1.6882922865027461</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="30">
         <v>18.681381249847327</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="30">
         <v>1.7628119813458687</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="30">
         <v>22.465408049744905</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="30">
         <v>4.9186260559120676</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="30">
         <v>20.982485932840646</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="30">
         <v>2.9693301873396694</v>
       </c>
     </row>
@@ -2085,142 +2088,142 @@
       <c r="A42" s="20">
         <v>2014</v>
       </c>
-      <c r="B42" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="23">
+      <c r="B42" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="31">
         <v>-1.7448022621509462</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="25">
+      <c r="B43" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="30">
         <v>3.672030702855178</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="25">
+      <c r="B44" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="30">
         <v>-3.0721657649173784</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="25">
+      <c r="B45" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="30">
         <v>-3.0182342663512385</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="25">
+      <c r="B46" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="30">
         <v>0.64798484499630771</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="25">
+      <c r="B47" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="30">
         <v>-0.48027747485250849</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="25">
+      <c r="B48" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="30">
         <v>-3.856373396143653</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="25">
+      <c r="B49" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="30">
         <v>-4.646540835091983</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="25">
+      <c r="B50" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="30">
         <v>-1.5758721940225651</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="25">
+      <c r="B51" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="30">
         <v>-2.3582574745903417</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="25">
+      <c r="B52" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="30">
         <v>0.57291336876788002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" s="25">
+      <c r="B53" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="30">
         <v>-5.1791422811558689</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="25">
+      <c r="B54" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="30">
         <v>-1.0058318246483733</v>
       </c>
     </row>
@@ -2228,142 +2231,142 @@
       <c r="A55" s="20">
         <v>2015</v>
       </c>
-      <c r="B55" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="23">
+      <c r="B55" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="31">
         <v>1.7158312195387548</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="30">
         <v>7.2624170877117367</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="30">
         <v>-1.4141556777358066</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="30">
         <v>10.205019415309469</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="30">
         <v>3.8162615130878041</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="30">
         <v>8.4567058402521766</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="30">
         <v>2.8911886689321431</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="30">
         <v>6.333917998255334</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="30">
         <v>0.48431175627521306</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="30">
         <v>8.6346325506411183</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="30">
         <v>1.7836637130637767</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="30">
         <v>6.9193036616377324</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="30">
         <v>0.35188154517935555</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="30">
         <v>14.682847518215446</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="30">
         <v>7.2508381748788375</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="26">
+      <c r="B63" s="30">
         <v>9.3327416134792998</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="30">
         <v>1.7821362836211163</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B64" s="26">
+      <c r="B64" s="30">
         <v>6.4275007317756705</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="30">
         <v>-0.5318629380783646</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="25">
+      <c r="B65" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="30">
         <v>1.7860705934264809</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="25">
+      <c r="B66" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="30">
         <v>6.8834889070060079</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="25">
+      <c r="B67" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="30">
         <v>-3.5332268244495535</v>
       </c>
     </row>
@@ -2371,142 +2374,142 @@
       <c r="A68" s="20">
         <v>2016</v>
       </c>
-      <c r="B68" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="23">
+      <c r="B68" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="31">
         <v>-7.164795923901357</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B69" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="25">
+      <c r="B69" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="30">
         <v>-2.6888025280167094</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B70" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="25">
+      <c r="B70" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="30">
         <v>1.1675382160851955</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B71" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="25">
+      <c r="B71" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="30">
         <v>-6.873755906803181</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B72" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="25">
+      <c r="B72" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="30">
         <v>-5.2625667927722048</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="29" t="s">
+      <c r="A73" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B73" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="25">
+      <c r="B73" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="30">
         <v>-11.675871637540691</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="29" t="s">
+      <c r="A74" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B74" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="25">
+      <c r="B74" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="30">
         <v>-8.3037058436280731</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B75" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="25">
+      <c r="B75" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="30">
         <v>-9.3031241526560837</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="29" t="s">
+      <c r="A76" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="25">
+      <c r="B76" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="30">
         <v>-10.217737572323093</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="29" t="s">
+      <c r="A77" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B77" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="25">
+      <c r="B77" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="30">
         <v>-5.8535371495342936</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" s="25">
+      <c r="B78" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="30">
         <v>-9.3668966066696164</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="25">
+      <c r="B79" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="30">
         <v>-10.49337566602826</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B80" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="25">
+      <c r="B80" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="30">
         <v>-5.2537378015719005</v>
       </c>
     </row>
@@ -2514,142 +2517,142 @@
       <c r="A81" s="20">
         <v>2017</v>
       </c>
-      <c r="B81" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" s="23">
+      <c r="B81" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="31">
         <v>-2.9973844432228613</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" s="25">
+      <c r="B82" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="30">
         <v>-6.3119956028720781</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="25">
+      <c r="B83" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="30">
         <v>-11.676372987723461</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" s="25">
+      <c r="B84" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="30">
         <v>-5.379612458264182</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" s="25">
+      <c r="B85" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="30">
         <v>-0.46445577772389335</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B86" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" s="25">
+      <c r="B86" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="30">
         <v>-1.5911246628848796</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B87" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" s="25">
+      <c r="B87" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="30">
         <v>-1.3656019352247917</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B88" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" s="25">
+      <c r="B88" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="30">
         <v>-2.3404516621850058</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" s="25">
+      <c r="B89" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" s="30">
         <v>-1.1627734650836663</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="29" t="s">
+      <c r="A90" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B90" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" s="25">
+      <c r="B90" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="30">
         <v>0.67460219384938291</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="29" t="s">
+      <c r="A91" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" s="25">
+      <c r="B91" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="30">
         <v>-2.7724419208275841</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B92" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" s="25">
+      <c r="B92" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="30">
         <v>-2.2840032871451643</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="29" t="s">
+      <c r="A93" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B93" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="25">
+      <c r="B93" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="30">
         <v>-1.7551934757647381</v>
       </c>
     </row>
@@ -2657,109 +2660,109 @@
       <c r="A94" s="20">
         <v>2018</v>
       </c>
-      <c r="B94" s="24">
+      <c r="B94" s="31">
         <v>-2.9236697719512983</v>
       </c>
-      <c r="C94" s="23">
+      <c r="C94" s="31">
         <v>-2.4475300728348026</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="29" t="s">
+      <c r="A95" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B95" s="25">
+      <c r="B95" s="30">
         <v>-2.6782466940800775</v>
       </c>
-      <c r="C95" s="25">
+      <c r="C95" s="30">
         <v>-3.0319771362668058</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="29" t="s">
+      <c r="A96" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B96" s="25">
+      <c r="B96" s="30">
         <v>0.77006494440801099</v>
       </c>
-      <c r="C96" s="25">
+      <c r="C96" s="30">
         <v>0.66659602803362805</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="29" t="s">
+      <c r="A97" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B97" s="25">
+      <c r="B97" s="30">
         <v>7.3511703726851563</v>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="30">
         <v>7.2040692654919303</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B98" s="25">
+      <c r="B98" s="30">
         <v>-2.4422329960504419</v>
       </c>
-      <c r="C98" s="25">
+      <c r="C98" s="30">
         <v>-2.9777323159478009</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="29" t="s">
+      <c r="A99" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B99" s="25">
+      <c r="B99" s="30">
         <v>1.7221818295971802</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="30">
         <v>1.4904241024081832</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B100" s="25">
+      <c r="B100" s="30">
         <v>2.058650791285932</v>
       </c>
-      <c r="C100" s="25">
+      <c r="C100" s="30">
         <v>2.4737142315150784</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="29" t="s">
+      <c r="A101" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B101" s="25">
+      <c r="B101" s="30">
         <v>-2.9195455870385856</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="30">
         <v>-2.9048069784318176</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" s="29" t="s">
+      <c r="A102" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="25">
+      <c r="B102" s="30">
         <v>-4.1606440154696163</v>
       </c>
-      <c r="C102" s="25">
+      <c r="C102" s="30">
         <v>-3.9832457038099567</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="29" t="s">
+      <c r="A103" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B103" s="25">
+      <c r="B103" s="30">
         <v>-7.5846580913870643</v>
       </c>
-      <c r="C103" s="25">
+      <c r="C103" s="30">
         <v>-5.5016242779778128</v>
       </c>
     </row>
@@ -2767,10 +2770,10 @@
       <c r="A104" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="25">
+      <c r="B104" s="30">
         <v>-7.8042592780726565</v>
       </c>
-      <c r="C104" s="25">
+      <c r="C104" s="30">
         <v>-6.3711754989621339</v>
       </c>
     </row>
@@ -2778,10 +2781,10 @@
       <c r="A105" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B105" s="25">
+      <c r="B105" s="30">
         <v>-7.9128083257072106</v>
       </c>
-      <c r="C105" s="25">
+      <c r="C105" s="30">
         <v>-6.4900263192593126</v>
       </c>
     </row>
@@ -2789,10 +2792,10 @@
       <c r="A106" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B106" s="25">
+      <c r="B106" s="30">
         <v>-9.591253889972096</v>
       </c>
-      <c r="C106" s="25">
+      <c r="C106" s="30">
         <v>-8.4233367249454858</v>
       </c>
     </row>
@@ -2800,10 +2803,10 @@
       <c r="A107" s="20">
         <v>2019</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B107" s="31">
         <v>-8.9593718558007573</v>
       </c>
-      <c r="C107" s="23">
+      <c r="C107" s="31">
         <v>-7.7007842890598148</v>
       </c>
     </row>
@@ -2811,154 +2814,154 @@
       <c r="A108" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B108" s="25">
+      <c r="B108" s="30">
         <v>-9.0490539257974341</v>
       </c>
-      <c r="C108" s="25">
+      <c r="C108" s="30">
         <v>-8.0211730604016651</v>
       </c>
-      <c r="F108" s="27"/>
+      <c r="F108" s="26"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B109" s="25">
+      <c r="B109" s="30">
         <v>-9.0901144682281387</v>
       </c>
-      <c r="C109" s="25">
+      <c r="C109" s="30">
         <v>-7.8892391767351633</v>
       </c>
-      <c r="F109" s="27"/>
+      <c r="F109" s="26"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B110" s="25">
+      <c r="B110" s="30">
         <v>-12.776582650642753</v>
       </c>
-      <c r="C110" s="25">
+      <c r="C110" s="30">
         <v>-11.440820885993841</v>
       </c>
-      <c r="F110" s="27"/>
+      <c r="F110" s="26"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B111" s="25">
+      <c r="B111" s="30">
         <v>-8.7178083256830963</v>
       </c>
-      <c r="C111" s="25">
+      <c r="C111" s="30">
         <v>-7.0679408508950274</v>
       </c>
-      <c r="F111" s="27"/>
+      <c r="F111" s="26"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B112" s="25">
+      <c r="B112" s="30">
         <v>-12.487761762293692</v>
       </c>
-      <c r="C112" s="25">
+      <c r="C112" s="30">
         <v>-10.676371286657904</v>
       </c>
-      <c r="F112" s="27"/>
+      <c r="F112" s="26"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B113" s="25">
+      <c r="B113" s="30">
         <v>-11.948607805846079</v>
       </c>
-      <c r="C113" s="25">
+      <c r="C113" s="30">
         <v>-10.542424946647888</v>
       </c>
-      <c r="F113" s="27"/>
+      <c r="F113" s="26"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B114" s="25">
+      <c r="B114" s="30">
         <v>-11.095461044925647</v>
       </c>
-      <c r="C114" s="25">
+      <c r="C114" s="30">
         <v>-9.952754376977369</v>
       </c>
-      <c r="F114" s="27"/>
+      <c r="F114" s="26"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="25">
+      <c r="B115" s="30">
         <v>-8.4054634132041617</v>
       </c>
-      <c r="C115" s="25">
+      <c r="C115" s="30">
         <v>-5.7353361576213508</v>
       </c>
-      <c r="F115" s="27"/>
+      <c r="F115" s="26"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B116" s="25">
+      <c r="B116" s="30">
         <v>-9.1287943142614125</v>
       </c>
-      <c r="C116" s="25">
+      <c r="C116" s="30">
         <v>-8.3592934584614138</v>
       </c>
-      <c r="F116" s="27"/>
+      <c r="F116" s="26"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B117" s="25">
+      <c r="B117" s="30">
         <v>-3.5795396750110342</v>
       </c>
-      <c r="C117" s="25">
+      <c r="C117" s="30">
         <v>-2.1756548444385904</v>
       </c>
-      <c r="F117" s="27"/>
+      <c r="F117" s="26"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="30">
         <v>-5.4864096906503512</v>
       </c>
-      <c r="C118" s="25">
+      <c r="C118" s="30">
         <v>-4.6554585703992064</v>
       </c>
-      <c r="F118" s="27"/>
+      <c r="F118" s="26"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B119" s="25">
+      <c r="B119" s="30">
         <v>-5.1340980777680905</v>
       </c>
-      <c r="C119" s="25">
+      <c r="C119" s="30">
         <v>-5.3410528042406753</v>
       </c>
-      <c r="F119" s="27"/>
+      <c r="F119" s="26"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="20">
         <v>2020</v>
       </c>
-      <c r="B120" s="23">
+      <c r="B120" s="31">
         <v>3.0458247413440276</v>
       </c>
-      <c r="C120" s="23">
+      <c r="C120" s="31">
         <v>2.8164614071535254</v>
       </c>
     </row>
@@ -2966,10 +2969,10 @@
       <c r="A121" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B121" s="25">
+      <c r="B121" s="30">
         <v>-2.696457701047017</v>
       </c>
-      <c r="C121" s="25">
+      <c r="C121" s="30">
         <v>-2.9132666868169066</v>
       </c>
     </row>
@@ -2977,10 +2980,10 @@
       <c r="A122" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B122" s="25">
+      <c r="B122" s="30">
         <v>14.190874524756026</v>
       </c>
-      <c r="C122" s="25">
+      <c r="C122" s="30">
         <v>13.946845042934308</v>
       </c>
     </row>
@@ -2988,10 +2991,10 @@
       <c r="A123" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B123" s="31">
+      <c r="B123" s="30">
         <v>17.851368399296753</v>
       </c>
-      <c r="C123" s="31">
+      <c r="C123" s="30">
         <v>17.557473833862304</v>
       </c>
     </row>
@@ -2999,10 +3002,10 @@
       <c r="A124" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B124" s="31">
+      <c r="B124" s="30">
         <v>3.7895143426346367</v>
       </c>
-      <c r="C124" s="31">
+      <c r="C124" s="30">
         <v>3.8115025700465877</v>
       </c>
     </row>
@@ -3010,10 +3013,10 @@
       <c r="A125" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B125" s="31">
+      <c r="B125" s="30">
         <v>9.7630106009974895</v>
       </c>
-      <c r="C125" s="31">
+      <c r="C125" s="30">
         <v>9.7216995002056059</v>
       </c>
     </row>
@@ -3021,10 +3024,10 @@
       <c r="A126" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B126" s="31">
+      <c r="B126" s="30">
         <v>0.38284421288161674</v>
       </c>
-      <c r="C126" s="31">
+      <c r="C126" s="30">
         <v>0.72888068505378989</v>
       </c>
     </row>
@@ -3032,10 +3035,10 @@
       <c r="A127" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B127" s="31">
+      <c r="B127" s="30">
         <v>2.105158893696979</v>
       </c>
-      <c r="C127" s="31">
+      <c r="C127" s="30">
         <v>3.1277555527348566</v>
       </c>
     </row>
@@ -3043,10 +3046,10 @@
       <c r="A128" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B128" s="31">
+      <c r="B128" s="30">
         <v>-2.7995579653339986</v>
       </c>
-      <c r="C128" s="31">
+      <c r="C128" s="30">
         <v>-3.5518561794059544</v>
       </c>
     </row>
@@ -3054,10 +3057,10 @@
       <c r="A129" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B129" s="31">
+      <c r="B129" s="30">
         <v>-0.69872322575847967</v>
       </c>
-      <c r="C129" s="31">
+      <c r="C129" s="30">
         <v>-1.9116928677533562</v>
       </c>
     </row>
@@ -3065,10 +3068,10 @@
       <c r="A130" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B130" s="31">
+      <c r="B130" s="30">
         <v>-0.70410609526455614</v>
       </c>
-      <c r="C130" s="31">
+      <c r="C130" s="30">
         <v>-1.3489422978516297</v>
       </c>
     </row>
@@ -3076,10 +3079,10 @@
       <c r="A131" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B131" s="31">
+      <c r="B131" s="30">
         <v>-4.2889288778263808</v>
       </c>
-      <c r="C131" s="31">
+      <c r="C131" s="30">
         <v>-4.6231013566395358</v>
       </c>
     </row>
@@ -3087,10 +3090,10 @@
       <c r="A132" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B132" s="31">
+      <c r="B132" s="30">
         <v>-6.5228505958325744E-2</v>
       </c>
-      <c r="C132" s="31">
+      <c r="C132" s="30">
         <v>-0.32084083611805259</v>
       </c>
     </row>
@@ -3098,10 +3101,10 @@
       <c r="A133" s="20">
         <v>2021</v>
       </c>
-      <c r="B133" s="32">
+      <c r="B133" s="31">
         <v>-3.0966577823741237</v>
       </c>
-      <c r="C133" s="32">
+      <c r="C133" s="31">
         <v>-3.7302994725838978</v>
       </c>
     </row>
@@ -3109,10 +3112,10 @@
       <c r="A134" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B134" s="31">
+      <c r="B134" s="30">
         <v>3.8364369195386105</v>
       </c>
-      <c r="C134" s="31">
+      <c r="C134" s="30">
         <v>3.5842575639897678</v>
       </c>
     </row>
@@ -3120,10 +3123,10 @@
       <c r="A135" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B135" s="31">
+      <c r="B135" s="30">
         <v>-14.784698300999521</v>
       </c>
-      <c r="C135" s="31">
+      <c r="C135" s="30">
         <v>-15.502802091723755</v>
       </c>
     </row>
@@ -3131,10 +3134,10 @@
       <c r="A136" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B136" s="31">
+      <c r="B136" s="30">
         <v>-18.111597369863176</v>
       </c>
-      <c r="C136" s="31">
+      <c r="C136" s="30">
         <v>-18.201504189064856</v>
       </c>
     </row>
@@ -3142,10 +3145,10 @@
       <c r="A137" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B137" s="31">
+      <c r="B137" s="30">
         <v>-7.0585269340742158</v>
       </c>
-      <c r="C137" s="31">
+      <c r="C137" s="30">
         <v>-7.6647795174308309</v>
       </c>
     </row>
@@ -3153,10 +3156,10 @@
       <c r="A138" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B138" s="31">
+      <c r="B138" s="30">
         <v>-7.5487861515930561</v>
       </c>
-      <c r="C138" s="31">
+      <c r="C138" s="30">
         <v>-8.1424085447094452</v>
       </c>
     </row>
@@ -3164,10 +3167,10 @@
       <c r="A139" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B139" s="31">
+      <c r="B139" s="30">
         <v>-3.555541961772446</v>
       </c>
-      <c r="C139" s="31">
+      <c r="C139" s="30">
         <v>-4.4705645804093974</v>
       </c>
     </row>
@@ -3175,10 +3178,10 @@
       <c r="A140" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B140" s="31">
+      <c r="B140" s="30">
         <v>-1.2307329587253779</v>
       </c>
-      <c r="C140" s="31">
+      <c r="C140" s="30">
         <v>-2.9044210068939424</v>
       </c>
     </row>
@@ -3186,10 +3189,10 @@
       <c r="A141" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B141" s="31">
+      <c r="B141" s="30">
         <v>1.0869539971999131</v>
       </c>
-      <c r="C141" s="31">
+      <c r="C141" s="30">
         <v>0.16877338994918389</v>
       </c>
     </row>
@@ -3197,10 +3200,10 @@
       <c r="A142" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B142" s="31">
+      <c r="B142" s="30">
         <v>3.4251873193532623</v>
       </c>
-      <c r="C142" s="31">
+      <c r="C142" s="30">
         <v>2.9743453940644704</v>
       </c>
     </row>
@@ -3208,10 +3211,10 @@
       <c r="A143" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B143" s="31">
+      <c r="B143" s="30">
         <v>1.5456949970371836</v>
       </c>
-      <c r="C143" s="31">
+      <c r="C143" s="30">
         <v>0.54866630442826914</v>
       </c>
     </row>
@@ -3219,10 +3222,10 @@
       <c r="A144" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B144" s="31">
+      <c r="B144" s="30">
         <v>4.5551065410239122</v>
       </c>
-      <c r="C144" s="31">
+      <c r="C144" s="30">
         <v>4.2993143529159283</v>
       </c>
     </row>
@@ -3230,10 +3233,10 @@
       <c r="A145" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B145" s="31">
+      <c r="B145" s="30">
         <v>5.6843544124552281</v>
       </c>
-      <c r="C145" s="31">
+      <c r="C145" s="30">
         <v>5.4979873117792399</v>
       </c>
     </row>
@@ -3241,10 +3244,10 @@
       <c r="A146" s="20">
         <v>2022</v>
       </c>
-      <c r="B146" s="32">
+      <c r="B146" s="31">
         <v>1.1236265391741052</v>
       </c>
-      <c r="C146" s="32">
+      <c r="C146" s="31">
         <v>0.22782171179804855</v>
       </c>
     </row>
@@ -3252,10 +3255,10 @@
       <c r="A147" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B147" s="31">
+      <c r="B147" s="30">
         <v>-0.86648008989640424</v>
       </c>
-      <c r="C147" s="31">
+      <c r="C147" s="30">
         <v>-1.8252085875138158</v>
       </c>
     </row>
@@ -3263,10 +3266,10 @@
       <c r="A148" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B148" s="31">
+      <c r="B148" s="30">
         <v>3.1764240024917401</v>
       </c>
-      <c r="C148" s="31">
+      <c r="C148" s="30">
         <v>2.1429130150535824</v>
       </c>
     </row>
@@ -3274,10 +3277,10 @@
       <c r="A149" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B149" s="31">
+      <c r="B149" s="30">
         <v>0.16074164922470491</v>
       </c>
-      <c r="C149" s="31">
+      <c r="C149" s="30">
         <v>-0.51744265531086242</v>
       </c>
     </row>
@@ -3285,10 +3288,10 @@
       <c r="A150" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B150" s="31">
+      <c r="B150" s="30">
         <v>1.9908547183506986</v>
       </c>
-      <c r="C150" s="31">
+      <c r="C150" s="30">
         <v>1.3425317729376829</v>
       </c>
     </row>
@@ -3296,10 +3299,10 @@
       <c r="A151" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B151" s="31">
+      <c r="B151" s="30">
         <v>-0.61538051047924647</v>
       </c>
-      <c r="C151" s="31">
+      <c r="C151" s="30">
         <v>-1.5056406918402376</v>
       </c>
     </row>
@@ -3307,10 +3310,10 @@
       <c r="A152" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B152" s="31">
+      <c r="B152" s="30">
         <v>2.3501311753102661</v>
       </c>
-      <c r="C152" s="31">
+      <c r="C152" s="30">
         <v>1.3083422376921394</v>
       </c>
     </row>
@@ -3318,10 +3321,10 @@
       <c r="A153" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B153" s="31">
+      <c r="B153" s="30">
         <v>5.2373450422741552</v>
       </c>
-      <c r="C153" s="31">
+      <c r="C153" s="30">
         <v>4.0217398169438923</v>
       </c>
     </row>
@@ -3329,10 +3332,10 @@
       <c r="A154" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B154" s="31">
+      <c r="B154" s="30">
         <v>-8.9095724091692308E-2</v>
       </c>
-      <c r="C154" s="31">
+      <c r="C154" s="30">
         <v>-0.6760686247448966</v>
       </c>
     </row>
@@ -3340,10 +3343,10 @@
       <c r="A155" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B155" s="31">
+      <c r="B155" s="30">
         <v>1.0207128610358218</v>
       </c>
-      <c r="C155" s="31">
+      <c r="C155" s="30">
         <v>0.51626783865390546</v>
       </c>
     </row>
@@ -3351,10 +3354,10 @@
       <c r="A156" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B156" s="31">
+      <c r="B156" s="30">
         <v>0.31136408897254331</v>
       </c>
-      <c r="C156" s="31">
+      <c r="C156" s="30">
         <v>-0.71595798083413653</v>
       </c>
     </row>
@@ -3362,10 +3365,10 @@
       <c r="A157" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B157" s="31">
+      <c r="B157" s="30">
         <v>2.5613506522061957</v>
       </c>
-      <c r="C157" s="31">
+      <c r="C157" s="30">
         <v>1.2534787995985175</v>
       </c>
     </row>
@@ -3373,10 +3376,10 @@
       <c r="A158" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B158" s="31">
+      <c r="B158" s="30">
         <v>-1.211670539455989</v>
       </c>
-      <c r="C158" s="31">
+      <c r="C158" s="30">
         <v>-2.1042775171962291</v>
       </c>
     </row>
@@ -3384,10 +3387,10 @@
       <c r="A159" s="20">
         <v>2023</v>
       </c>
-      <c r="B159" s="32">
+      <c r="B159" s="31">
         <v>1.8040296647150234</v>
       </c>
-      <c r="C159" s="32">
+      <c r="C159" s="31">
         <v>2.2912277033328765</v>
       </c>
     </row>
@@ -3395,10 +3398,10 @@
       <c r="A160" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B160" s="31">
+      <c r="B160" s="30">
         <v>2.6812830181589753</v>
       </c>
-      <c r="C160" s="31">
+      <c r="C160" s="30">
         <v>2.3095335954363083</v>
       </c>
     </row>
@@ -3406,10 +3409,10 @@
       <c r="A161" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B161" s="31">
+      <c r="B161" s="30">
         <v>1.7391493336371688</v>
       </c>
-      <c r="C161" s="31">
+      <c r="C161" s="30">
         <v>2.4634134124337459</v>
       </c>
     </row>
@@ -3417,10 +3420,10 @@
       <c r="A162" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B162" s="31">
+      <c r="B162" s="30">
         <v>4.9050917553357998</v>
       </c>
-      <c r="C162" s="31">
+      <c r="C162" s="30">
         <v>3.9234701594574206</v>
       </c>
     </row>
@@ -3428,10 +3431,10 @@
       <c r="A163" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B163" s="31">
+      <c r="B163" s="30">
         <v>3.7509683780349024</v>
       </c>
-      <c r="C163" s="31">
+      <c r="C163" s="30">
         <v>2.7927195596578969</v>
       </c>
     </row>
@@ -3439,10 +3442,10 @@
       <c r="A164" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B164" s="31">
+      <c r="B164" s="30">
         <v>-9.070385577824025E-2</v>
       </c>
-      <c r="C164" s="31">
+      <c r="C164" s="30">
         <v>-1.0042103730752872</v>
       </c>
     </row>
@@ -3450,10 +3453,10 @@
       <c r="A165" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B165" s="31">
+      <c r="B165" s="30">
         <v>0.36468590623863761</v>
       </c>
-      <c r="C165" s="31">
+      <c r="C165" s="30">
         <v>-0.63501354241786157</v>
       </c>
     </row>
@@ -3461,10 +3464,10 @@
       <c r="A166" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B166" s="31">
+      <c r="B166" s="30">
         <v>-1.2468252603098473</v>
       </c>
-      <c r="C166" s="31">
+      <c r="C166" s="30">
         <v>-1.3724533377253434</v>
       </c>
     </row>
@@ -3472,10 +3475,10 @@
       <c r="A167" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B167" s="31">
+      <c r="B167" s="30">
         <v>4.0297372366129069</v>
       </c>
-      <c r="C167" s="31">
+      <c r="C167" s="30">
         <v>4.5435192359973398</v>
       </c>
     </row>
@@ -3483,10 +3486,10 @@
       <c r="A168" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B168" s="31">
+      <c r="B168" s="30">
         <v>1.8870875020798872</v>
       </c>
-      <c r="C168" s="31">
+      <c r="C168" s="30">
         <v>2.7102854111286767</v>
       </c>
     </row>
@@ -3494,10 +3497,10 @@
       <c r="A169" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B169" s="31">
+      <c r="B169" s="30">
         <v>6.5477472392057257</v>
       </c>
-      <c r="C169" s="31">
+      <c r="C169" s="30">
         <v>8.6423857473833632</v>
       </c>
     </row>
@@ -3505,10 +3508,10 @@
       <c r="A170" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B170" s="31">
+      <c r="B170" s="30">
         <v>1.7238441976645813</v>
       </c>
-      <c r="C170" s="31">
+      <c r="C170" s="30">
         <v>4.4815138252685127</v>
       </c>
     </row>
@@ -3516,10 +3519,10 @@
       <c r="A171" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B171" s="31">
+      <c r="B171" s="30">
         <v>-3.7084521038872942</v>
       </c>
-      <c r="C171" s="31">
+      <c r="C171" s="30">
         <v>-0.89020151586457485</v>
       </c>
     </row>
@@ -3527,10 +3530,10 @@
       <c r="A172" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B172" s="32">
+      <c r="B172" s="31">
         <v>-5.4452771286398693</v>
       </c>
-      <c r="C172" s="32">
+      <c r="C172" s="31">
         <v>-8.8028756838881108</v>
       </c>
     </row>
@@ -3538,10 +3541,10 @@
       <c r="A173" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B173" s="31">
+      <c r="B173" s="30">
         <v>-9.8274256548845926</v>
       </c>
-      <c r="C173" s="31">
+      <c r="C173" s="30">
         <v>-10.075958246295414</v>
       </c>
     </row>
@@ -3549,10 +3552,10 @@
       <c r="A174" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B174" s="31">
+      <c r="B174" s="30">
         <v>-4.6841914146010684</v>
       </c>
-      <c r="C174" s="31">
+      <c r="C174" s="30">
         <v>-7.6188046402548393</v>
       </c>
     </row>
@@ -3560,10 +3563,10 @@
       <c r="A175" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B175" s="31">
+      <c r="B175" s="30">
         <v>-5.138214737095181</v>
       </c>
-      <c r="C175" s="31">
+      <c r="C175" s="30">
         <v>-8.4920162826650714</v>
       </c>
     </row>
@@ -3571,21 +3574,21 @@
       <c r="A176" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B176" s="31">
+      <c r="B176" s="30">
         <v>-11.14605258779482</v>
       </c>
-      <c r="C176" s="31">
+      <c r="C176" s="30">
         <v>-13.762794845050962</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B177" s="31">
+        <v>2</v>
+      </c>
+      <c r="B177" s="30">
         <v>-3.659488587569093</v>
       </c>
-      <c r="C177" s="31">
+      <c r="C177" s="30">
         <v>-6.450763163067375</v>
       </c>
     </row>
@@ -3593,10 +3596,10 @@
       <c r="A178" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B178" s="31">
+      <c r="B178" s="30">
         <v>-2.6533265975572706</v>
       </c>
-      <c r="C178" s="31">
+      <c r="C178" s="30">
         <v>-4.809359975210703</v>
       </c>
     </row>
@@ -3604,10 +3607,10 @@
       <c r="A179" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B179" s="31">
+      <c r="B179" s="30">
         <v>-6.7544675951070161</v>
       </c>
-      <c r="C179" s="31">
+      <c r="C179" s="30">
         <v>-9.3279837676101032</v>
       </c>
     </row>
@@ -3615,10 +3618,10 @@
       <c r="A180" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B180" s="31">
+      <c r="B180" s="30">
         <v>-3.1186552143895985</v>
       </c>
-      <c r="C180" s="31">
+      <c r="C180" s="30">
         <v>-6.9726893844789473</v>
       </c>
     </row>
@@ -3626,10 +3629,10 @@
       <c r="A181" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B181" s="31">
+      <c r="B181" s="30">
         <v>-4.3016820197295802</v>
       </c>
-      <c r="C181" s="31">
+      <c r="C181" s="30">
         <v>-8.3341787611350586</v>
       </c>
     </row>
@@ -3637,10 +3640,10 @@
       <c r="A182" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B182" s="31">
+      <c r="B182" s="30">
         <v>-10.976825147988677</v>
       </c>
-      <c r="C182" s="31">
+      <c r="C182" s="30">
         <v>-15.057968901456299</v>
       </c>
     </row>
@@ -3648,10 +3651,10 @@
       <c r="A183" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B183" s="31">
+      <c r="B183" s="30">
         <v>-3.1671996115822942</v>
       </c>
-      <c r="C183" s="31">
+      <c r="C183" s="30">
         <v>-8.4678156485272211</v>
       </c>
     </row>
@@ -3659,10 +3662,10 @@
       <c r="A184" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B184" s="31">
+      <c r="B184" s="30">
         <v>-0.12844396462980967</v>
       </c>
-      <c r="C184" s="31">
+      <c r="C184" s="30">
         <v>-5.8219434853522323</v>
       </c>
     </row>
@@ -3670,10 +3673,10 @@
       <c r="A185" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B185" s="23">
+      <c r="B185" s="31">
         <v>2.6299210860754929</v>
       </c>
-      <c r="C185" s="32">
+      <c r="C185" s="31">
         <v>2.2354819936383885</v>
       </c>
     </row>
@@ -3681,10 +3684,10 @@
       <c r="A186" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B186" s="25">
+      <c r="B186" s="30">
         <v>6.424782454333311</v>
       </c>
-      <c r="C186" s="31">
+      <c r="C186" s="30">
         <v>3.0445682534996132</v>
       </c>
     </row>
@@ -3692,10 +3695,10 @@
       <c r="A187" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B187" s="25">
+      <c r="B187" s="30">
         <v>0.913928113577267</v>
       </c>
-      <c r="C187" s="31">
+      <c r="C187" s="30">
         <v>0.10798249085102185</v>
       </c>
     </row>
@@ -3703,10 +3706,10 @@
       <c r="A188" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B188" s="25">
+      <c r="B188" s="30">
         <v>3.5594193431058185</v>
       </c>
-      <c r="C188" s="31">
+      <c r="C188" s="30">
         <v>3.9779845516348056</v>
       </c>
     </row>
@@ -3714,10 +3717,10 @@
       <c r="A189" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B189" s="25">
+      <c r="B189" s="30">
         <v>7.3209336111032419</v>
       </c>
-      <c r="C189" s="31">
+      <c r="C189" s="30">
         <v>7.4284852936586931</v>
       </c>
     </row>
@@ -3725,10 +3728,10 @@
       <c r="A190" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B190" s="25">
+      <c r="B190" s="30">
         <v>5.0424707305149141</v>
       </c>
-      <c r="C190" s="31">
+      <c r="C190" s="30">
         <v>5.458554768353796</v>
       </c>
     </row>
@@ -3736,10 +3739,10 @@
       <c r="A191" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B191" s="25">
+      <c r="B191" s="30">
         <v>1.9735890338509643</v>
       </c>
-      <c r="C191" s="31">
+      <c r="C191" s="30">
         <v>1.6025749154301439</v>
       </c>
     </row>
@@ -3747,10 +3750,10 @@
       <c r="A192" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B192" s="25">
+      <c r="B192" s="30">
         <v>2.1751890017045916</v>
       </c>
-      <c r="C192" s="31">
+      <c r="C192" s="30">
         <v>1.7852340508690112</v>
       </c>
     </row>
@@ -3758,10 +3761,10 @@
       <c r="A193" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B193" s="25">
+      <c r="B193" s="30">
         <v>-0.87815838823711578</v>
       </c>
-      <c r="C193" s="31">
+      <c r="C193" s="30">
         <v>-0.86472629992971894</v>
       </c>
     </row>
@@ -3769,10 +3772,10 @@
       <c r="A194" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B194" s="25">
+      <c r="B194" s="30">
         <v>0.46373997202231454</v>
       </c>
-      <c r="C194" s="31">
+      <c r="C194" s="30">
         <v>0.20772392982373322</v>
       </c>
     </row>
@@ -3780,10 +3783,10 @@
       <c r="A195" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B195" s="25">
+      <c r="B195" s="30">
         <v>3.7954455884269489</v>
       </c>
-      <c r="C195" s="31">
+      <c r="C195" s="30">
         <v>3.2231531066716501</v>
       </c>
     </row>
@@ -3791,10 +3794,10 @@
       <c r="A196" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B196" s="25">
+      <c r="B196" s="30">
         <v>-0.5123341711536944</v>
       </c>
-      <c r="C196" s="31">
+      <c r="C196" s="30">
         <v>-1.0772294600705945</v>
       </c>
     </row>
@@ -3802,10 +3805,10 @@
       <c r="A197" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B197" s="25">
+      <c r="B197" s="30">
         <v>2.1381949853111148</v>
       </c>
-      <c r="C197" s="31">
+      <c r="C197" s="30">
         <v>2.2370658176845692</v>
       </c>
     </row>
@@ -3814,16 +3817,16 @@
         <v>2026</v>
       </c>
       <c r="B198" s="25"/>
-      <c r="C198" s="31"/>
+      <c r="C198" s="30"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B199" s="25">
-        <v>0.56529296004366181</v>
-      </c>
-      <c r="C199" s="31">
+      <c r="B199" s="30">
+        <v>0.56529296004372842</v>
+      </c>
+      <c r="C199" s="30">
         <v>0.31093287260046676</v>
       </c>
     </row>
@@ -3831,10 +3834,10 @@
       <c r="A200" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B200" s="25">
-        <v>-0.12368980474311009</v>
-      </c>
-      <c r="C200" s="31">
+      <c r="B200" s="30">
+        <v>-0.12266014719521934</v>
+      </c>
+      <c r="C200" s="30">
         <v>-0.58755797637353169</v>
       </c>
     </row>
@@ -3842,10 +3845,10 @@
       <c r="A201" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B201" s="25">
-        <v>-1.4584831237162588</v>
-      </c>
-      <c r="C201" s="31">
+      <c r="B201" s="30">
+        <v>-1.4577414223466367</v>
+      </c>
+      <c r="C201" s="30">
         <v>-2.0136773701644683</v>
       </c>
     </row>
@@ -3853,53 +3856,64 @@
       <c r="A202" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B202" s="25">
-        <v>-0.76856188125520308</v>
-      </c>
-      <c r="C202" s="31">
+      <c r="B202" s="30">
+        <v>-0.76742699772127665</v>
+      </c>
+      <c r="C202" s="30">
         <v>-1.3788194803648346</v>
       </c>
     </row>
-    <row r="203" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A203" s="35" t="s">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A203" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B203" s="30">
+        <v>1.1462407775851169</v>
+      </c>
+      <c r="C203" s="30">
+        <v>0.14737887304852038</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A204" s="36" t="s">
         <v>63</v>
-      </c>
-      <c r="B203" s="35"/>
-      <c r="C203" s="35"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A204" s="36" t="s">
-        <v>20</v>
       </c>
       <c r="B204" s="36"/>
       <c r="C204" s="36"/>
-      <c r="D204" s="30"/>
-      <c r="E204" s="30"/>
-      <c r="F204" s="30"/>
-      <c r="H204" s="30"/>
-      <c r="I204" s="30"/>
-      <c r="J204" s="30"/>
-    </row>
-    <row r="205" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="34" t="s">
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A205" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B205" s="37"/>
+      <c r="C205" s="37"/>
+      <c r="D205" s="29"/>
+      <c r="E205" s="29"/>
+      <c r="F205" s="29"/>
+      <c r="H205" s="29"/>
+      <c r="I205" s="29"/>
+      <c r="J205" s="29"/>
+    </row>
+    <row r="206" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B205" s="34"/>
-      <c r="C205" s="34"/>
-    </row>
-    <row r="206" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="33" t="s">
+      <c r="B206" s="35"/>
+      <c r="C206" s="35"/>
+    </row>
+    <row r="207" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B206" s="33"/>
-      <c r="C206" s="33"/>
+      <c r="B207" s="34"/>
+      <c r="C207" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3924,10 +3938,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="44"/>
+      <c r="B1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -3970,7 +3984,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3978,7 +3992,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>41</v>
       </c>

--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10830"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,7 +254,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/mayo de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/junio de 2026</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J207"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="21" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B178" s="30">
         <v>-2.6533265975572706</v>
@@ -3824,7 +3824,7 @@
         <v>23</v>
       </c>
       <c r="B199" s="30">
-        <v>0.56529296004372842</v>
+        <v>0.56529296004370622</v>
       </c>
       <c r="C199" s="30">
         <v>0.31093287260046676</v>
@@ -3835,7 +3835,7 @@
         <v>24</v>
       </c>
       <c r="B200" s="30">
-        <v>-0.12266014719521934</v>
+        <v>-0.12266014719520824</v>
       </c>
       <c r="C200" s="30">
         <v>-0.58755797637353169</v>
@@ -3846,7 +3846,7 @@
         <v>25</v>
       </c>
       <c r="B201" s="30">
-        <v>-1.4577414223466367</v>
+        <v>-1.4577414223466589</v>
       </c>
       <c r="C201" s="30">
         <v>-2.0136773701644683</v>
@@ -3857,7 +3857,7 @@
         <v>26</v>
       </c>
       <c r="B202" s="30">
-        <v>-0.76742699772127665</v>
+        <v>-0.76733740875721823</v>
       </c>
       <c r="C202" s="30">
         <v>-1.3788194803648346</v>
@@ -3868,52 +3868,63 @@
         <v>27</v>
       </c>
       <c r="B203" s="30">
-        <v>1.1462407775851169</v>
+        <v>1.1463233008342399</v>
       </c>
       <c r="C203" s="30">
         <v>0.14737887304852038</v>
       </c>
     </row>
-    <row r="204" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A204" s="36" t="s">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A204" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B204" s="30">
+        <v>-1.5406980284155103</v>
+      </c>
+      <c r="C204" s="30">
+        <v>-2.2404135904803057</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A205" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B204" s="36"/>
-      <c r="C204" s="36"/>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A205" s="37" t="s">
+      <c r="B205" s="36"/>
+      <c r="C205" s="36"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A206" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B205" s="37"/>
-      <c r="C205" s="37"/>
-      <c r="D205" s="29"/>
-      <c r="E205" s="29"/>
-      <c r="F205" s="29"/>
-      <c r="H205" s="29"/>
-      <c r="I205" s="29"/>
-      <c r="J205" s="29"/>
-    </row>
-    <row r="206" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="35" t="s">
+      <c r="B206" s="37"/>
+      <c r="C206" s="37"/>
+      <c r="D206" s="29"/>
+      <c r="E206" s="29"/>
+      <c r="F206" s="29"/>
+      <c r="H206" s="29"/>
+      <c r="I206" s="29"/>
+      <c r="J206" s="29"/>
+    </row>
+    <row r="207" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="35"/>
-      <c r="C206" s="35"/>
-    </row>
-    <row r="207" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="34" t="s">
+      <c r="B207" s="35"/>
+      <c r="C207" s="35"/>
+    </row>
+    <row r="208" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B207" s="34"/>
-      <c r="C207" s="34"/>
+      <c r="B208" s="34"/>
+      <c r="C208" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A207:C207"/>
+    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3984,7 +3995,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3992,7 +4003,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
@@ -4000,7 +4011,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>42</v>
       </c>
@@ -4017,7 +4028,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>44</v>
       </c>
